--- a/stories/arbres/ATOM-AUT.AFF.001-07.xlsx
+++ b/stories/arbres/ATOM-AUT.AFF.001-07.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Clara va au parc avec papa. Papa pose le sac ouvert. Papa dit : on met la gourde. On met le chapeau. On met le doudou. C'est ce que l'adulte a dit. Clara prend la gourde. Elle la met dans le sac. Le sac est bleu. Clara prend le chapeau. Elle le met dans le sac. Elle prend le doudou. Elle le met dans le sac. Papa dit : tu as mis ce que l'adulte a dit. Clara ferme le sac. Elle le porte. À l'entrée, elle vérifie. Gourde, chapeau, doudou. Tout est dans le sac. Papa sourit. Clara a préparé son sac.</t>
+          <t>Clara va au parc avec papa. Papa pose le sac ouvert. On met la gourde. On met le chapeau. On met le doudou. C'est ce que l'adulte a dit. Clara prend la gourde. Elle la met dans le sac. Le sac est bleu. Clara prend le chapeau. Elle le met dans le sac. Elle prend le doudou. Elle le met dans le sac. Tu as mis ce que l'adulte a dit. Clara ferme le sac. Elle le porte. À l'entrée, elle vérifie. Gourde, chapeau, doudou. Tout est dans le sac. Papa sourit. Clara a préparé son sac.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,15 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Clara va au parc avec papa. Papa pose le sac ouvert.
+papa|On met la gourde. On met le chapeau. On met le doudou. C'est ce que l'adulte a dit.
+narrateur|Clara prend la gourde. Elle la met dans le sac. Le sac est bleu. Clara prend le chapeau. Elle le met dans le sac. Elle prend le doudou. Elle le met dans le sac.
+papa|Tu as mis ce que l'adulte a dit.
+narrateur|Clara ferme le sac. Elle le porte. À l'entrée, elle vérifie. Gourde, chapeau, doudou. Tout est dans le sac. Papa sourit. Clara a préparé son sac.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1469,6 +1494,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Clara prépare le sac. Que met-elle ?</t>
         </is>
       </c>
     </row>
@@ -1637,6 +1667,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Clara a préparé son sac. Elle a mis ce que l'adulte a dit. Papa était là.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1799,6 +1834,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Clara porte le sac. Papa ouvre la porte.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1961,6 +2001,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1979,7 +2024,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1996,6 +2041,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-AUT.AFF.001-07.xlsx
+++ b/stories/arbres/ATOM-AUT.AFF.001-07.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1314,6 +1319,11 @@
 narrateur|Clara ferme le sac. Elle le porte. À l'entrée, elle vérifie. Gourde, chapeau, doudou. Tout est dans le sac. Papa sourit. Clara a préparé son sac.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1501,6 +1511,7 @@
           <t>narrateur|Clara prépare le sac. Que met-elle ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1672,6 +1683,7 @@
           <t>narrateur|Clara a préparé son sac. Elle a mis ce que l'adulte a dit. Papa était là.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1839,6 +1851,7 @@
           <t>narrateur|Clara porte le sac. Papa ouvre la porte.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2006,6 +2019,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2024,7 +2038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2048,6 +2062,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2062,7 +2090,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2249,6 +2277,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-AUT.AFF.001-07.xlsx
+++ b/stories/arbres/ATOM-AUT.AFF.001-07.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Clara prépare son sac</t>
+          <t>Le sac du matin</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Le sac du matin est encore froid contre la porte. Aniss y met la gourde, le chapeau et le doudou. Il vérifie à l'entrée. Papa ouvre la porte.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Clara va au parc avec papa. Papa pose le sac ouvert. On met la gourde. On met le chapeau. On met le doudou. C'est ce que l'adulte a dit. Clara prend la gourde. Elle la met dans le sac. Le sac est bleu. Clara prend le chapeau. Elle le met dans le sac. Elle prend le doudou. Elle le met dans le sac. Tu as mis ce que l'adulte a dit. Clara ferme le sac. Elle le porte. À l'entrée, elle vérifie. Gourde, chapeau, doudou. Tout est dans le sac. Papa sourit. Clara a préparé son sac.</t>
+          <t>Le sac du matin est encore un peu froid. Il sent le tissu. Il est posé contre le bas de la porte. Les crochets cliquettent un peu. Un oiseau chante dehors. Aniss, on va au parc. En ce moment, Aniss s'accroupit. Papa pose le sac ouvert. Le sac est bleu. On met la gourde. On met le chapeau. On met le doudou. C'est ce que l'adulte a dit. La gourde, le chapeau, le doudou. Aniss prend la gourde. Elle est fraîche. Tu la mets dans le sac ? Aniss la met dans le sac. Bravo. La gourde est dedans. Aniss prend le chapeau. Le bord est un peu souple. Tu le mets dans le sac ? Aniss le met dans le sac. Bravo. Le chapeau est dedans. Aniss prend le doudou. Il sent le coton. Il est tout doux. Tu le mets dans le sac ? Aniss le met dans le sac. Tu as mis ce que l'adulte a dit. Aniss ferme le sac. Ça fait zzz. Il le porte. À l'entrée, il vérifie. Gourde, chapeau, doudou. Tout est dans le sac. Bravo. Tu as fait du bon travail. Le sac est prêt ? Oui, papa. Le sac du matin n'est plus froid.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,11 +1324,46 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Clara va au parc avec papa. Papa pose le sac ouvert.
-papa|On met la gourde. On met le chapeau. On met le doudou. C'est ce que l'adulte a dit.
-narrateur|Clara prend la gourde. Elle la met dans le sac. Le sac est bleu. Clara prend le chapeau. Elle le met dans le sac. Elle prend le doudou. Elle le met dans le sac.
+          <t>narrateur|Le sac du matin est encore un peu froid.
+narrateur|Il sent le tissu.
+narrateur|Il est posé contre le bas de la porte.
+narrateur|Les crochets cliquettent un peu.
+narrateur|Un oiseau chante dehors.
+papa|Aniss, on va au parc.
+narrateur|En ce moment, Aniss s'accroupit.
+narrateur|Papa pose le sac ouvert.
+narrateur|Le sac est bleu.
+papa|On met la gourde.
+papa|On met le chapeau.
+papa|On met le doudou.
+papa|C'est ce que l'adulte a dit.
+enfant-m|La gourde, le chapeau, le doudou.
+narrateur|Aniss prend la gourde.
+narrateur|Elle est fraîche.
+papa|Tu la mets dans le sac ?
+narrateur|Aniss la met dans le sac.
+papa|Bravo. La gourde est dedans.
+narrateur|Aniss prend le chapeau.
+narrateur|Le bord est un peu souple.
+papa|Tu le mets dans le sac ?
+narrateur|Aniss le met dans le sac.
+papa|Bravo. Le chapeau est dedans.
+narrateur|Aniss prend le doudou.
+narrateur|Il sent le coton.
+enfant-m|Il est tout doux.
+papa|Tu le mets dans le sac ?
+narrateur|Aniss le met dans le sac.
 papa|Tu as mis ce que l'adulte a dit.
-narrateur|Clara ferme le sac. Elle le porte. À l'entrée, elle vérifie. Gourde, chapeau, doudou. Tout est dans le sac. Papa sourit. Clara a préparé son sac.</t>
+narrateur|Aniss ferme le sac.
+narrateur|Ça fait zzz.
+narrateur|Il le porte.
+narrateur|À l'entrée, il vérifie.
+enfant-m|Gourde, chapeau, doudou.
+narrateur|Tout est dans le sac.
+papa|Bravo. Tu as fait du bon travail.
+papa|Le sac est prêt ?
+enfant-m|Oui, papa.
+narrateur|Le sac du matin n'est plus froid.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -1348,7 +1395,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Clara prépare le sac. Que met-elle ?</t>
+          <t>Aniss prépare le sac. Que met-il ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1508,10 +1555,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Clara prépare le sac. Que met-elle ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Aniss prépare le sac.
+narrateur|Que met-il ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1536,7 +1583,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Clara a préparé son sac. Elle a mis ce que l'adulte a dit. Papa était là.</t>
+          <t>Aniss a préparé son sac. Il a mis ce que l'adulte a dit. La gourde, le chapeau, le doudou. Tu as fini de préparer le sac ? Oui. Bravo. Le sac est prêt. Aniss tient la sangle. Elle n'est plus froide. L'oiseau chante encore.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1680,10 +1727,17 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Clara a préparé son sac. Elle a mis ce que l'adulte a dit. Papa était là.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Aniss a préparé son sac.
+narrateur|Il a mis ce que l'adulte a dit.
+narrateur|La gourde, le chapeau, le doudou.
+papa|Tu as fini de préparer le sac ?
+enfant-m|Oui.
+papa|Bravo. Le sac est prêt.
+narrateur|Aniss tient la sangle.
+narrateur|Elle n'est plus froide.
+narrateur|L'oiseau chante encore.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1708,7 +1762,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Clara porte le sac. Papa ouvre la porte.</t>
+          <t>Aniss porte le sac. On ouvre la porte ? Papa ouvre la porte. Tu as ton sac, Aniss ? Oui, papa. Bravo. L'air sent l'herbe du parc. Ils sortent.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1848,10 +1902,16 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Clara porte le sac. Papa ouvre la porte.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Aniss porte le sac.
+papa|On ouvre la porte ?
+narrateur|Papa ouvre la porte.
+papa|Tu as ton sac, Aniss ?
+enfant-m|Oui, papa.
+papa|Bravo.
+narrateur|L'air sent l'herbe du parc.
+narrateur|Ils sortent.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1876,7 +1936,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Le sac du matin voyage sur le dos. Gourde, chapeau, doudou. Le sac est prêt. Oui. Tu as mis ce que l'adulte a dit. Bravo, Aniss. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2016,10 +2076,14 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>narrateur|Le sac du matin voyage sur le dos.
+narrateur|Gourde, chapeau, doudou.
+enfant-m|Le sac est prêt.
+papa|Oui. Tu as mis ce que l'adulte a dit.
+papa|Bravo, Aniss.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2038,7 +2102,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2076,6 +2140,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-AUT.AFF.001-07.xlsx
+++ b/stories/arbres/ATOM-AUT.AFF.001-07.xlsx
@@ -1184,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Le sac du matin est encore un peu froid. Il sent le tissu. Il est posé contre le bas de la porte. Les crochets cliquettent un peu. Un oiseau chante dehors. Aniss, on va au parc. En ce moment, Aniss s'accroupit. Papa pose le sac ouvert. Le sac est bleu. On met la gourde. On met le chapeau. On met le doudou. C'est ce que l'adulte a dit. La gourde, le chapeau, le doudou. Aniss prend la gourde. Elle est fraîche. Tu la mets dans le sac ? Aniss la met dans le sac. Bravo. La gourde est dedans. Aniss prend le chapeau. Le bord est un peu souple. Tu le mets dans le sac ? Aniss le met dans le sac. Bravo. Le chapeau est dedans. Aniss prend le doudou. Il sent le coton. Il est tout doux. Tu le mets dans le sac ? Aniss le met dans le sac. Tu as mis ce que l'adulte a dit. Aniss ferme le sac. Ça fait zzz. Il le porte. À l'entrée, il vérifie. Gourde, chapeau, doudou. Tout est dans le sac. Bravo. Tu as fait du bon travail. Le sac est prêt ? Oui, papa. Le sac du matin n'est plus froid.</t>
+          <t>Le sac du matin est encore un peu froid. Il sent le tissu. Il est posé contre le bas de la porte. Les crochets cliquettent un peu. Un oiseau chante dehors. Le tapis de l'entrée est un peu rêche. Une chaussure attend près du sac. Aniss, on va au parc. En ce moment, Aniss s'accroupit. Papa pose le sac ouvert. Le sac est bleu. On met la gourde. On met le chapeau. On met le doudou. C'est ce que l'adulte a dit. La gourde, le chapeau, le doudou. Aniss prend la gourde. Elle est fraîche. Tu la mets dans le sac ? Aniss la met dans le sac. Bravo. La gourde est dedans. Aniss prend le chapeau. Le bord est un peu souple. Tu le mets dans le sac ? Aniss le met dans le sac. Bravo. Le chapeau est dedans. Aniss prend le doudou. Il sent le coton. Il est tout doux. Tu le mets dans le sac ? Aniss le met dans le sac. Tu as mis ce que l'adulte a dit. Aniss ferme le sac. Ça fait zzz. Il le porte. À l'entrée, il vérifie. Gourde, chapeau, doudou. Tout est dans le sac. Bravo. Tu as fait du bon travail. Le sac est prêt ? Oui, papa. Le sac du matin n'est plus froid.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1329,6 +1329,8 @@
 narrateur|Il est posé contre le bas de la porte.
 narrateur|Les crochets cliquettent un peu.
 narrateur|Un oiseau chante dehors.
+narrateur|Le tapis de l'entrée est un peu rêche.
+narrateur|Une chaussure attend près du sac.
 papa|Aniss, on va au parc.
 narrateur|En ce moment, Aniss s'accroupit.
 narrateur|Papa pose le sac ouvert.
@@ -1762,7 +1764,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Aniss porte le sac. On ouvre la porte ? Papa ouvre la porte. Tu as ton sac, Aniss ? Oui, papa. Bravo. L'air sent l'herbe du parc. Ils sortent.</t>
+          <t>Aniss porte le sac. On met tes chaussures ? Aniss enfile ses chaussures. Tu as fini tes chaussures ? Oui, papa. Bravo. On ouvre la porte ? Papa ouvre la porte. Tu as ton sac, Aniss ? Oui, papa. Bravo. L'air sent l'herbe du parc. Ils sortent.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1903,6 +1905,11 @@
       <c r="AW5" t="inlineStr">
         <is>
           <t>narrateur|Aniss porte le sac.
+papa|On met tes chaussures ?
+narrateur|Aniss enfile ses chaussures.
+papa|Tu as fini tes chaussures ?
+enfant-m|Oui, papa.
+papa|Bravo.
 papa|On ouvre la porte ?
 narrateur|Papa ouvre la porte.
 papa|Tu as ton sac, Aniss ?
@@ -2102,7 +2109,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2145,6 +2152,34 @@
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>

--- a/stories/arbres/ATOM-AUT.AFF.001-07.xlsx
+++ b/stories/arbres/ATOM-AUT.AFF.001-07.xlsx
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Le sac du matin</t>
+          <t>L'oiseau d'Aniss</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>entrée de la maison</t>
+          <t>cuisine, entrée, parc</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Clara, papa</t>
+          <t>Aniss, papa</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>120</v>
+        <v>180</v>
       </c>
     </row>
     <row r="19">
@@ -704,7 +704,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>165</v>
+        <v>240</v>
       </c>
     </row>
     <row r="20">
@@ -714,7 +714,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>210</v>
+        <v>320</v>
       </c>
     </row>
     <row r="21">
@@ -841,7 +841,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Le sac du matin est encore froid contre la porte. Aniss y met la gourde, le chapeau et le doudou. Il vérifie à l'entrée. Papa ouvre la porte.</t>
+          <t>Aniss veut voir l'oiseau au parc. Papa dit gourde, chapeau, doudou. Le chapeau glisse. Le doudou est sur la chaise. Aniss met ce que papa a dit. L'oiseau chante dans le grand arbre.</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Le sac du matin est encore un peu froid. Il sent le tissu. Il est posé contre le bas de la porte. Les crochets cliquettent un peu. Un oiseau chante dehors. Le tapis de l'entrée est un peu rêche. Une chaussure attend près du sac. Aniss, on va au parc. En ce moment, Aniss s'accroupit. Papa pose le sac ouvert. Le sac est bleu. On met la gourde. On met le chapeau. On met le doudou. C'est ce que l'adulte a dit. La gourde, le chapeau, le doudou. Aniss prend la gourde. Elle est fraîche. Tu la mets dans le sac ? Aniss la met dans le sac. Bravo. La gourde est dedans. Aniss prend le chapeau. Le bord est un peu souple. Tu le mets dans le sac ? Aniss le met dans le sac. Bravo. Le chapeau est dedans. Aniss prend le doudou. Il sent le coton. Il est tout doux. Tu le mets dans le sac ? Aniss le met dans le sac. Tu as mis ce que l'adulte a dit. Aniss ferme le sac. Ça fait zzz. Il le porte. À l'entrée, il vérifie. Gourde, chapeau, doudou. Tout est dans le sac. Bravo. Tu as fait du bon travail. Le sac est prêt ? Oui, papa. Le sac du matin n'est plus froid.</t>
+          <t>Une tartine croustille sur l'assiette. Ça sent le beurre. Un oiseau chante déjà dehors. Les crochets cliquettent un peu. Le tapis de l'entrée est un peu rêche. Une miette tombe près de la tasse. Papa verse un peu d'eau. L'eau fait un bruit clair. La tartine a un bord doré. Elle croustille, papa. Oui. Une dernière bouchée. Aniss, tu entends l'oiseau ? Oui. Je veux le voir au parc. On y va. Avec le sac. En ce moment, Aniss s'accroupit. Le sac est posé contre la porte. Il est un peu froid. Le sac est bleu. On met la gourde, le chapeau, le doudou. C'est ce que l'adulte a dit. La gourde, le chapeau, le doudou. Aniss prend la gourde. Elle est fraîche. Il la met dans le sac. Il prend le chapeau. Le bord est un peu souple. Le chapeau glisse par terre. Il est tombé. Tu le ramasses. Puis dans le sac. Aniss ramasse le chapeau. Il le met dans le sac. Et le doudou ? Le doudou n'est pas près des chaussures.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Clara va au parc avec papa. Papa pose le &lt;emphasis level="moderate"&gt;sac&lt;/emphasis&gt; ouvert. Papa dit : on met la gourde. On met le chapeau. On met le doudou. C'est ce que l'adulte a dit. Clara prend la gourde. Elle la met dans le sac. Le sac est bleu. Clara prend le chapeau. Elle le met dans le sac. Elle prend le doudou. Elle le met dans le sac. Papa dit : tu as mis ce que l'adulte a dit. Clara ferme le sac. Elle le porte. À l'entrée, elle vérifie. Gourde, chapeau, doudou. Tout est dans le sac. Papa sourit. Clara a préparé son sac.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Une tartine croustille sur l'assiette. Ça sent le beurre. Un oiseau chante déjà dehors. Les crochets cliquettent un peu. Le tapis de l'entrée est un peu rêche. Une miette tombe près de la tasse. Papa verse un peu d'eau. L'eau fait un bruit clair. La tartine a un bord doré. Elle croustille, papa. Oui. Une dernière bouchée. Aniss, tu entends l'oiseau ? Oui. Je veux le voir au parc. On y va. Avec le sac. En ce moment, Aniss s'accroupit. Le sac est posé contre la porte. Il est un peu froid. Le sac est bleu. On met la gourde, le chapeau, le doudou. C'est ce que l'adulte a dit. La gourde, le chapeau, le doudou. Aniss prend la gourde. Elle est fraîche. Il la met dans le sac. Il prend le chapeau. Le bord est un peu souple. Le chapeau glisse par terre. Il est tombé. Tu le ramasses. Puis dans le sac. Aniss ramasse le chapeau. Il le met dans le sac. Et le doudou ? Le doudou n'est pas près des chaussures.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1324,48 +1324,39 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Le sac du matin est encore un peu froid.
-narrateur|Il sent le tissu.
-narrateur|Il est posé contre le bas de la porte.
+          <t>narrateur|Une tartine croustille sur l'assiette.
+narrateur|Ça sent le beurre.
+narrateur|Un oiseau chante déjà dehors.
 narrateur|Les crochets cliquettent un peu.
-narrateur|Un oiseau chante dehors.
 narrateur|Le tapis de l'entrée est un peu rêche.
-narrateur|Une chaussure attend près du sac.
-papa|Aniss, on va au parc.
+narrateur|Une miette tombe près de la tasse.
+narrateur|Papa verse un peu d'eau.
+narrateur|L'eau fait un bruit clair.
+narrateur|La tartine a un bord doré.
+enfant-m|Elle croustille, papa.
+papa|Oui. Une dernière bouchée.
+papa|Aniss, tu entends l'oiseau ?
+enfant-m|Oui. Je veux le voir au parc.
+papa|On y va. Avec le sac.
 narrateur|En ce moment, Aniss s'accroupit.
-narrateur|Papa pose le sac ouvert.
+narrateur|Le sac est posé contre la porte.
+narrateur|Il est un peu froid.
 narrateur|Le sac est bleu.
-papa|On met la gourde.
-papa|On met le chapeau.
-papa|On met le doudou.
+papa|On met la gourde, le chapeau, le doudou.
 papa|C'est ce que l'adulte a dit.
 enfant-m|La gourde, le chapeau, le doudou.
 narrateur|Aniss prend la gourde.
 narrateur|Elle est fraîche.
-papa|Tu la mets dans le sac ?
-narrateur|Aniss la met dans le sac.
-papa|Bravo. La gourde est dedans.
-narrateur|Aniss prend le chapeau.
+narrateur|Il la met dans le sac.
+narrateur|Il prend le chapeau.
 narrateur|Le bord est un peu souple.
-papa|Tu le mets dans le sac ?
-narrateur|Aniss le met dans le sac.
-papa|Bravo. Le chapeau est dedans.
-narrateur|Aniss prend le doudou.
-narrateur|Il sent le coton.
-enfant-m|Il est tout doux.
-papa|Tu le mets dans le sac ?
-narrateur|Aniss le met dans le sac.
-papa|Tu as mis ce que l'adulte a dit.
-narrateur|Aniss ferme le sac.
-narrateur|Ça fait zzz.
-narrateur|Il le porte.
-narrateur|À l'entrée, il vérifie.
-enfant-m|Gourde, chapeau, doudou.
-narrateur|Tout est dans le sac.
-papa|Bravo. Tu as fait du bon travail.
-papa|Le sac est prêt ?
-enfant-m|Oui, papa.
-narrateur|Le sac du matin n'est plus froid.</t>
+narrateur|Le chapeau glisse par terre.
+enfant-m|Il est tombé.
+papa|Tu le ramasses. Puis dans le sac.
+narrateur|Aniss ramasse le chapeau.
+narrateur|Il le met dans le sac.
+enfant-m|Et le doudou ?
+narrateur|Le doudou n'est pas près des chaussures.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -1397,12 +1388,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Aniss prépare le sac. Que met-il ?</t>
+          <t>Aniss prépare le sac. Où met-il les affaires ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Clara prépare le &lt;emphasis level="moderate"&gt;sac&lt;/emphasis&gt;. Que met-elle ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Aniss prépare le sac. Où met-il les affaires ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1417,7 +1408,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>le sac | dans le sac | mettre | ce que papa a dit | gourde</t>
+          <t>le sac | dans le sac | il met | mettre | ce que papa a dit | gourde | chapeau | doudou</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -1432,7 +1423,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Papa a dit quoi mettre. Où Clara le met-elle ?</t>
+          <t>Il met les affaires dans le sac. Où les met-il ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1481,7 +1472,7 @@
         <v>0.86</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1558,7 +1549,7 @@
       <c r="AW3" t="inlineStr">
         <is>
           <t>narrateur|Aniss prépare le sac.
-narrateur|Que met-il ?</t>
+narrateur|Où met-il les affaires ?</t>
         </is>
       </c>
     </row>
@@ -1585,12 +1576,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Aniss a préparé son sac. Il a mis ce que l'adulte a dit. La gourde, le chapeau, le doudou. Tu as fini de préparer le sac ? Oui. Bravo. Le sac est prêt. Aniss tient la sangle. Elle n'est plus froide. L'oiseau chante encore.</t>
+          <t>Le doudou est sur la chaise de la cuisine. Il sent le coton. Il est tout doux. Aniss le met dans le sac. Tu as mis ce que l'adulte a dit. Aniss ferme le sac. Ça fait zzz. Il le porte. À l'entrée, il vérifie. Gourde, chapeau, doudou. Tout est dans le sac. Le sac est prêt ? Oui, papa. La sangle n'est plus froide. Tu as fini ta tartine ? Oui, papa. Alors on va voir l'oiseau.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Clara a préparé son &lt;emphasis level="moderate"&gt;sac&lt;/emphasis&gt;. Elle a mis ce que l'adulte a dit. Papa était là.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le doudou est sur la chaise de la cuisine. Il sent le coton. Il est tout doux. Aniss le met dans le sac. Tu as mis ce que l'adulte a dit. Aniss ferme le sac. Ça fait zzz. Il le porte. À l'entrée, il vérifie. Gourde, chapeau, doudou. Tout est dans le sac. Le sac est prêt ? Oui, papa. La sangle n'est plus froide. Tu as fini ta tartine ? Oui, papa. Alors on va voir l'oiseau.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1729,15 +1720,23 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Aniss a préparé son sac.
-narrateur|Il a mis ce que l'adulte a dit.
-narrateur|La gourde, le chapeau, le doudou.
-papa|Tu as fini de préparer le sac ?
-enfant-m|Oui.
-papa|Bravo. Le sac est prêt.
-narrateur|Aniss tient la sangle.
-narrateur|Elle n'est plus froide.
-narrateur|L'oiseau chante encore.</t>
+          <t>narrateur|Le doudou est sur la chaise de la cuisine.
+narrateur|Il sent le coton.
+narrateur|Il est tout doux.
+narrateur|Aniss le met dans le sac.
+papa|Tu as mis ce que l'adulte a dit.
+narrateur|Aniss ferme le sac.
+narrateur|Ça fait zzz.
+narrateur|Il le porte.
+narrateur|À l'entrée, il vérifie.
+enfant-m|Gourde, chapeau, doudou.
+narrateur|Tout est dans le sac.
+papa|Le sac est prêt ?
+enfant-m|Oui, papa.
+narrateur|La sangle n'est plus froide.
+papa|Tu as fini ta tartine ?
+enfant-m|Oui, papa.
+papa|Alors on va voir l'oiseau.</t>
         </is>
       </c>
     </row>
@@ -1764,12 +1763,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Aniss porte le sac. On met tes chaussures ? Aniss enfile ses chaussures. Tu as fini tes chaussures ? Oui, papa. Bravo. On ouvre la porte ? Papa ouvre la porte. Tu as ton sac, Aniss ? Oui, papa. Bravo. L'air sent l'herbe du parc. Ils sortent.</t>
+          <t>On met tes chaussures. Aniss enfile ses chaussures. Tu as fini tes chaussures ? Oui, papa. On ouvre la porte. Papa ouvre la porte. L'air sent l'herbe du parc. L'oiseau chante encore. Je l'entends, papa. Oui. Il est dans le grand arbre. Ils sortent. Le sac tape doucement. La tartine n'est plus sur l'assiette. Ils s'arrêtent sous le grand arbre. Une feuille bouge. Il est là-haut. Oui. On écoute encore un peu. L'oiseau fait un petit cri. Aniss lève le menton.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Clara porte le &lt;emphasis level="moderate"&gt;sac&lt;/emphasis&gt;. Papa ouvre la porte.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>On met tes chaussures. Aniss enfile ses chaussures. Tu as fini tes chaussures ? Oui, papa. On ouvre la porte. Papa ouvre la porte. L'air sent l'herbe du parc. L'oiseau chante encore. Je l'entends, papa. Oui. Il est dans le grand arbre. Ils sortent. Le sac tape doucement. La tartine n'est plus sur l'assiette. Ils s'arrêtent sous le grand arbre. Une feuille bouge. Il est là-haut. Oui. On écoute encore un peu. L'oiseau fait un petit cri. Aniss lève le menton.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1904,19 +1903,25 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Aniss porte le sac.
-papa|On met tes chaussures ?
+          <t>papa|On met tes chaussures.
 narrateur|Aniss enfile ses chaussures.
 papa|Tu as fini tes chaussures ?
 enfant-m|Oui, papa.
-papa|Bravo.
-papa|On ouvre la porte ?
+papa|On ouvre la porte.
 narrateur|Papa ouvre la porte.
-papa|Tu as ton sac, Aniss ?
-enfant-m|Oui, papa.
-papa|Bravo.
 narrateur|L'air sent l'herbe du parc.
-narrateur|Ils sortent.</t>
+narrateur|L'oiseau chante encore.
+enfant-m|Je l'entends, papa.
+papa|Oui. Il est dans le grand arbre.
+narrateur|Ils sortent.
+narrateur|Le sac tape doucement.
+narrateur|La tartine n'est plus sur l'assiette.
+narrateur|Ils s'arrêtent sous le grand arbre.
+narrateur|Une feuille bouge.
+enfant-m|Il est là-haut.
+papa|Oui. On écoute encore un peu.
+narrateur|L'oiseau fait un petit cri.
+narrateur|Aniss lève le menton.</t>
         </is>
       </c>
     </row>
@@ -1943,12 +1948,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Le sac du matin voyage sur le dos. Gourde, chapeau, doudou. Le sac est prêt. Oui. Tu as mis ce que l'adulte a dit. Bravo, Aniss. L'histoire est finie.</t>
+          <t>Le sac voyage sur le dos d'Aniss. Gourde, chapeau, doudou. Le sac est prêt. Oui. Tu as mis ce que l'adulte a dit. L'oiseau chante plus fort. Aniss reste un moment, tout calme. On l'a vu. On l'a entendu. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le sac voyage sur le dos d'Aniss. Gourde, chapeau, doudou. Le sac est prêt. Oui. Tu as mis ce que l'adulte a dit. L'oiseau chante plus fort. Aniss reste un moment, tout calme. On l'a vu. On l'a entendu. L'histoire est finie.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2011,7 +2016,7 @@
         <v>0.88</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2083,11 +2088,13 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|Le sac du matin voyage sur le dos.
+          <t>narrateur|Le sac voyage sur le dos d'Aniss.
 narrateur|Gourde, chapeau, doudou.
 enfant-m|Le sac est prêt.
 papa|Oui. Tu as mis ce que l'adulte a dit.
-papa|Bravo, Aniss.
+narrateur|L'oiseau chante plus fort.
+narrateur|Aniss reste un moment, tout calme.
+papa|On l'a vu. On l'a entendu.
 narrateur|L'histoire est finie.</t>
         </is>
       </c>
@@ -2109,7 +2116,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2182,6 +2189,13 @@
       <c r="A10" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-AUT.AFF.001-07.xlsx
+++ b/stories/arbres/ATOM-AUT.AFF.001-07.xlsx
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>L'oiseau d'Aniss</t>
+          <t>La plume d'Aniss</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Aniss veut voir l'oiseau au parc. Papa dit gourde, chapeau, doudou. Le chapeau glisse. Le doudou est sur la chaise. Aniss met ce que papa a dit. L'oiseau chante dans le grand arbre.</t>
+          <t>Aniss veut l'oiseau du bois. Le chapeau tombe, le doudou est sur la chaise. Il range, marche, une plume lui chatouille le doigt.</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Une tartine croustille sur l'assiette. Ça sent le beurre. Un oiseau chante déjà dehors. Les crochets cliquettent un peu. Le tapis de l'entrée est un peu rêche. Une miette tombe près de la tasse. Papa verse un peu d'eau. L'eau fait un bruit clair. La tartine a un bord doré. Elle croustille, papa. Oui. Une dernière bouchée. Aniss, tu entends l'oiseau ? Oui. Je veux le voir au parc. On y va. Avec le sac. En ce moment, Aniss s'accroupit. Le sac est posé contre la porte. Il est un peu froid. Le sac est bleu. On met la gourde, le chapeau, le doudou. C'est ce que l'adulte a dit. La gourde, le chapeau, le doudou. Aniss prend la gourde. Elle est fraîche. Il la met dans le sac. Il prend le chapeau. Le bord est un peu souple. Le chapeau glisse par terre. Il est tombé. Tu le ramasses. Puis dans le sac. Aniss ramasse le chapeau. Il le met dans le sac. Et le doudou ? Le doudou n'est pas près des chaussures.</t>
+          <t>Une branche frotte le chemin du bois. Les aiguilles de pin sentent le chaud. Une tartine croustille sur l'assiette. Ça sent le beurre. Un oiseau chante déjà dehors. Les crochets cliquettent un peu. Le tapis de l'entrée est un peu rêche. Une miette tombe près de la tasse. Papa verse un peu d'eau. L'eau fait un bruit clair. La tartine a un bord doré. Elle croustille, papa. Une dernière bouchée ? Oui. Aniss, tu entends l'oiseau ? Oui, je veux le voir dans le bois. On y va, avec le sac. En ce moment, Aniss s'accroupit. Le sac est posé contre la porte. Il est un peu froid. Le sac est bleu. Prends de l'eau, le chemin est long. Aniss prend la gourde. Elle est fraîche. Il la met dans le sac. Le chapeau aussi, les branches piquent. Aniss prend le chapeau. Le bord est un peu souple. Le chapeau glisse par terre. Il est tombé. Tu le ramasses, puis dans le sac. Aniss ramasse le chapeau. Il le met dans le sac. Et le doudou ? Le doudou n'est pas près des chaussures. Regarde la chaise de la cuisine.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Une tartine croustille sur l'assiette. Ça sent le beurre. Un oiseau chante déjà dehors. Les crochets cliquettent un peu. Le tapis de l'entrée est un peu rêche. Une miette tombe près de la tasse. Papa verse un peu d'eau. L'eau fait un bruit clair. La tartine a un bord doré. Elle croustille, papa. Oui. Une dernière bouchée. Aniss, tu entends l'oiseau ? Oui. Je veux le voir au parc. On y va. Avec le sac. En ce moment, Aniss s'accroupit. Le sac est posé contre la porte. Il est un peu froid. Le sac est bleu. On met la gourde, le chapeau, le doudou. C'est ce que l'adulte a dit. La gourde, le chapeau, le doudou. Aniss prend la gourde. Elle est fraîche. Il la met dans le sac. Il prend le chapeau. Le bord est un peu souple. Le chapeau glisse par terre. Il est tombé. Tu le ramasses. Puis dans le sac. Aniss ramasse le chapeau. Il le met dans le sac. Et le doudou ? Le doudou n'est pas près des chaussures.</t>
+          <t>Une branche frotte le chemin du bois. Les aiguilles de pin sentent le chaud. Une tartine croustille sur l'assiette. Ça sent le beurre. Un oiseau chante déjà dehors. Les crochets cliquettent un peu. Le tapis de l'entrée est un peu rêche. Une miette tombe près de la tasse. Papa verse un peu d'eau. L'eau fait un bruit clair. La tartine a un bord doré. Elle croustille, papa. Une dernière bouchée ? Oui. Aniss, tu entends l'oiseau ? Oui, je veux le voir dans le bois. On y va, avec le sac. En ce moment, Aniss s'accroupit. Le sac est posé contre la porte. Il est un peu froid. Le sac est bleu. Prends de l'eau, le chemin est long. Aniss prend la gourde. Elle est fraîche. Il la met dans le sac. Le chapeau aussi, les branches piquent. Aniss prend le chapeau. Le bord est un peu souple. Le chapeau glisse par terre. Il est tombé. Tu le ramasses, puis dans le sac. Aniss ramasse le chapeau. Il le met dans le sac. Et le doudou ? Le doudou n'est pas près des chaussures. Regarde la chaise de la cuisine.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1252,7 +1252,7 @@
         <v>0.92</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1324,7 +1324,9 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Une tartine croustille sur l'assiette.
+          <t>narrateur|Une branche frotte le chemin du bois.
+narrateur|Les aiguilles de pin sentent le chaud.
+narrateur|Une tartine croustille sur l'assiette.
 narrateur|Ça sent le beurre.
 narrateur|Un oiseau chante déjà dehors.
 narrateur|Les crochets cliquettent un peu.
@@ -1334,34 +1336,35 @@
 narrateur|L'eau fait un bruit clair.
 narrateur|La tartine a un bord doré.
 enfant-m|Elle croustille, papa.
-papa|Oui. Une dernière bouchée.
+papa|Une dernière bouchée ?
+enfant-m|Oui.
 papa|Aniss, tu entends l'oiseau ?
-enfant-m|Oui. Je veux le voir au parc.
-papa|On y va. Avec le sac.
+enfant-m|Oui, je veux le voir dans le bois.
+papa|On y va, avec le sac.
 narrateur|En ce moment, Aniss s'accroupit.
 narrateur|Le sac est posé contre la porte.
 narrateur|Il est un peu froid.
 narrateur|Le sac est bleu.
-papa|On met la gourde, le chapeau, le doudou.
-papa|C'est ce que l'adulte a dit.
-enfant-m|La gourde, le chapeau, le doudou.
+papa|Prends de l'eau, le chemin est long.
 narrateur|Aniss prend la gourde.
 narrateur|Elle est fraîche.
 narrateur|Il la met dans le sac.
-narrateur|Il prend le chapeau.
+papa|Le chapeau aussi, les branches piquent.
+narrateur|Aniss prend le chapeau.
 narrateur|Le bord est un peu souple.
 narrateur|Le chapeau glisse par terre.
 enfant-m|Il est tombé.
-papa|Tu le ramasses. Puis dans le sac.
+papa|Tu le ramasses, puis dans le sac.
 narrateur|Aniss ramasse le chapeau.
 narrateur|Il le met dans le sac.
 enfant-m|Et le doudou ?
-narrateur|Le doudou n'est pas près des chaussures.</t>
+narrateur|Le doudou n'est pas près des chaussures.
+papa|Regarde la chaise de la cuisine.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>enfants_parc</t>
+          <t>oiseau</t>
         </is>
       </c>
     </row>
@@ -1408,7 +1411,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>le sac | dans le sac | il met | mettre | ce que papa a dit | gourde | chapeau | doudou</t>
+          <t>le sac | dans le sac | il met | elle met | mettre</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -1423,7 +1426,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Il met les affaires dans le sac. Où les met-il ?</t>
+          <t>Il met les affaires dans le sac. Où les met Aniss ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1576,12 +1579,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Le doudou est sur la chaise de la cuisine. Il sent le coton. Il est tout doux. Aniss le met dans le sac. Tu as mis ce que l'adulte a dit. Aniss ferme le sac. Ça fait zzz. Il le porte. À l'entrée, il vérifie. Gourde, chapeau, doudou. Tout est dans le sac. Le sac est prêt ? Oui, papa. La sangle n'est plus froide. Tu as fini ta tartine ? Oui, papa. Alors on va voir l'oiseau.</t>
+          <t>Le doudou est sur la chaise de la cuisine. Il sent le coton. Il est tout doux. Aniss le met dans le sac. Te voilà. Merci, Aniss. Aniss ferme le sac. Ça fait zzz. Il le porte. Le sac est prêt ? Oui, papa. La sangle n'est plus froide. Tu as fini ta tartine ? Oui, papa. Alors on va voir l'oiseau. Une miette reste près de la tasse. On la laisse pour plus tard.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Le doudou est sur la chaise de la cuisine. Il sent le coton. Il est tout doux. Aniss le met dans le sac. Tu as mis ce que l'adulte a dit. Aniss ferme le sac. Ça fait zzz. Il le porte. À l'entrée, il vérifie. Gourde, chapeau, doudou. Tout est dans le sac. Le sac est prêt ? Oui, papa. La sangle n'est plus froide. Tu as fini ta tartine ? Oui, papa. Alors on va voir l'oiseau.</t>
+          <t>Le doudou est sur la chaise de la cuisine. Il sent le coton. Il est tout doux. Aniss le met dans le sac. Te voilà. Merci, Aniss. Aniss ferme le sac. Ça fait zzz. Il le porte. Le sac est prêt ? Oui, papa. La sangle n'est plus froide. Tu as fini ta tartine ? Oui, papa. Alors on va voir l'oiseau. Une miette reste près de la tasse. On la laisse pour plus tard.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1644,7 +1647,7 @@
         <v>0.92</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1724,19 +1727,19 @@
 narrateur|Il sent le coton.
 narrateur|Il est tout doux.
 narrateur|Aniss le met dans le sac.
-papa|Tu as mis ce que l'adulte a dit.
+enfant-m|Te voilà.
+papa|Merci, Aniss.
 narrateur|Aniss ferme le sac.
 narrateur|Ça fait zzz.
 narrateur|Il le porte.
-narrateur|À l'entrée, il vérifie.
-enfant-m|Gourde, chapeau, doudou.
-narrateur|Tout est dans le sac.
 papa|Le sac est prêt ?
 enfant-m|Oui, papa.
 narrateur|La sangle n'est plus froide.
 papa|Tu as fini ta tartine ?
 enfant-m|Oui, papa.
-papa|Alors on va voir l'oiseau.</t>
+papa|Alors on va voir l'oiseau.
+narrateur|Une miette reste près de la tasse.
+papa|On la laisse pour plus tard.</t>
         </is>
       </c>
     </row>
@@ -1763,12 +1766,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>On met tes chaussures. Aniss enfile ses chaussures. Tu as fini tes chaussures ? Oui, papa. On ouvre la porte. Papa ouvre la porte. L'air sent l'herbe du parc. L'oiseau chante encore. Je l'entends, papa. Oui. Il est dans le grand arbre. Ils sortent. Le sac tape doucement. La tartine n'est plus sur l'assiette. Ils s'arrêtent sous le grand arbre. Une feuille bouge. Il est là-haut. Oui. On écoute encore un peu. L'oiseau fait un petit cri. Aniss lève le menton.</t>
+          <t>On met tes chaussures. Aniss enfile ses chaussures. Tu as fini tes chaussures ? Oui, papa. On ouvre la porte. Papa ouvre la porte. L'air sent le pin et l'herbe sèche. L'oiseau chante encore. Je l'entends, papa. Oui, il est dans le grand arbre. Ils marchent sur le chemin du bois. Le sac tape doucement. La tartine n'est plus sur l'assiette. Ils s'arrêtent sous le grand arbre. Une feuille bouge. Il est là-haut. Oui, on écoute encore un peu. L'oiseau fait un petit cri. Aniss lève le menton. Une plume grise est dans l'herbe. Pour moi ? Tu la prends tout doux ? Aniss ramasse la plume. Elle est légère, presque rien.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>On met tes chaussures. Aniss enfile ses chaussures. Tu as fini tes chaussures ? Oui, papa. On ouvre la porte. Papa ouvre la porte. L'air sent l'herbe du parc. L'oiseau chante encore. Je l'entends, papa. Oui. Il est dans le grand arbre. Ils sortent. Le sac tape doucement. La tartine n'est plus sur l'assiette. Ils s'arrêtent sous le grand arbre. Une feuille bouge. Il est là-haut. Oui. On écoute encore un peu. L'oiseau fait un petit cri. Aniss lève le menton.</t>
+          <t>On met tes chaussures. Aniss enfile ses chaussures. Tu as fini tes chaussures ? Oui, papa. On ouvre la porte. Papa ouvre la porte. L'air sent le pin et l'herbe sèche. L'oiseau chante encore. Je l'entends, papa. Oui, il est dans le grand arbre. Ils marchent sur le chemin du bois. Le sac tape doucement. La tartine n'est plus sur l'assiette. Ils s'arrêtent sous le grand arbre. Une feuille bouge. Il est là-haut. Oui, on écoute encore un peu. L'oiseau fait un petit cri. Aniss lève le menton. Une plume grise est dans l'herbe. Pour moi ? Tu la prends tout doux ? Aniss ramasse la plume. Elle est légère, presque rien.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1831,7 +1834,7 @@
         <v>0.92</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1909,19 +1912,24 @@
 enfant-m|Oui, papa.
 papa|On ouvre la porte.
 narrateur|Papa ouvre la porte.
-narrateur|L'air sent l'herbe du parc.
+narrateur|L'air sent le pin et l'herbe sèche.
 narrateur|L'oiseau chante encore.
 enfant-m|Je l'entends, papa.
-papa|Oui. Il est dans le grand arbre.
-narrateur|Ils sortent.
+papa|Oui, il est dans le grand arbre.
+narrateur|Ils marchent sur le chemin du bois.
 narrateur|Le sac tape doucement.
 narrateur|La tartine n'est plus sur l'assiette.
 narrateur|Ils s'arrêtent sous le grand arbre.
 narrateur|Une feuille bouge.
 enfant-m|Il est là-haut.
-papa|Oui. On écoute encore un peu.
+papa|Oui, on écoute encore un peu.
 narrateur|L'oiseau fait un petit cri.
-narrateur|Aniss lève le menton.</t>
+narrateur|Aniss lève le menton.
+narrateur|Une plume grise est dans l'herbe.
+enfant-m|Pour moi ?
+papa|Tu la prends tout doux ?
+narrateur|Aniss ramasse la plume.
+narrateur|Elle est légère, presque rien.</t>
         </is>
       </c>
     </row>
@@ -1948,12 +1956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Le sac voyage sur le dos d'Aniss. Gourde, chapeau, doudou. Le sac est prêt. Oui. Tu as mis ce que l'adulte a dit. L'oiseau chante plus fort. Aniss reste un moment, tout calme. On l'a vu. On l'a entendu. L'histoire est finie.</t>
+          <t>La plume chatouille le doigt d'Aniss. L'oiseau chante plus fort. On l'a vu. On l'a entendu. Le sac voyage sur le dos d'Aniss. Les aiguilles de pin sentent encore le chaud. Bravo, tu as préparé le chemin. Aniss reste un moment, tout calme, sous l'arbre.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Le sac voyage sur le dos d'Aniss. Gourde, chapeau, doudou. Le sac est prêt. Oui. Tu as mis ce que l'adulte a dit. L'oiseau chante plus fort. Aniss reste un moment, tout calme. On l'a vu. On l'a entendu. L'histoire est finie.</t>
+          <t>La plume chatouille le doigt d'Aniss. L'oiseau chante plus fort. On l'a vu. On l'a entendu. Le sac voyage sur le dos d'Aniss. Les aiguilles de pin sentent encore le chaud. Bravo, tu as préparé le chemin. Aniss reste un moment, tout calme, sous l'arbre.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2009,14 +2017,14 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA6" s="2" t="n">
         <v>0.88</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2088,14 +2096,14 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|Le sac voyage sur le dos d'Aniss.
-narrateur|Gourde, chapeau, doudou.
-enfant-m|Le sac est prêt.
-papa|Oui. Tu as mis ce que l'adulte a dit.
+          <t>narrateur|La plume chatouille le doigt d'Aniss.
 narrateur|L'oiseau chante plus fort.
-narrateur|Aniss reste un moment, tout calme.
-papa|On l'a vu. On l'a entendu.
-narrateur|L'histoire est finie.</t>
+enfant-m|On l'a vu.
+papa|On l'a entendu.
+narrateur|Le sac voyage sur le dos d'Aniss.
+narrateur|Les aiguilles de pin sentent encore le chaud.
+papa|Bravo, tu as préparé le chemin.
+narrateur|Aniss reste un moment, tout calme, sous l'arbre.</t>
         </is>
       </c>
     </row>
@@ -2116,7 +2124,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2194,6 +2202,13 @@
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>

--- a/stories/arbres/ATOM-AUT.AFF.001-07.xlsx
+++ b/stories/arbres/ATOM-AUT.AFF.001-07.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>cuisine, entrée, parc</t>
+          <t>maison au bord du bois puis chemin sous l'arbre</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-AUT.AFF.001-07.xlsx
+++ b/stories/arbres/ATOM-AUT.AFF.001-07.xlsx
@@ -1956,12 +1956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>La plume chatouille le doigt d'Aniss. L'oiseau chante plus fort. On l'a vu. On l'a entendu. Le sac voyage sur le dos d'Aniss. Les aiguilles de pin sentent encore le chaud. Bravo, tu as préparé le chemin. Aniss reste un moment, tout calme, sous l'arbre.</t>
+          <t>La plume chatouille le doigt d'Aniss. L'oiseau chante plus fort. On l'a vu. On l'a entendu. Le sac voyage sur le dos d'Aniss. Les aiguilles de pin sentent encore le chaud. Le doudou est chaud, contre toi. Aniss reste un moment, tout calme, sous l'arbre.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>La plume chatouille le doigt d'Aniss. L'oiseau chante plus fort. On l'a vu. On l'a entendu. Le sac voyage sur le dos d'Aniss. Les aiguilles de pin sentent encore le chaud. Bravo, tu as préparé le chemin. Aniss reste un moment, tout calme, sous l'arbre.</t>
+          <t>La plume chatouille le doigt d'Aniss. L'oiseau chante plus fort. On l'a vu. On l'a entendu. Le sac voyage sur le dos d'Aniss. Les aiguilles de pin sentent encore le chaud. Le doudou est chaud, contre toi. Aniss reste un moment, tout calme, sous l'arbre.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
 papa|On l'a entendu.
 narrateur|Le sac voyage sur le dos d'Aniss.
 narrateur|Les aiguilles de pin sentent encore le chaud.
-papa|Bravo, tu as préparé le chemin.
+papa|Le doudou est chaud, contre toi.
 narrateur|Aniss reste un moment, tout calme, sous l'arbre.</t>
         </is>
       </c>
@@ -2124,7 +2124,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A12"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2209,6 +2209,13 @@
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>

--- a/stories/arbres/ATOM-AUT.AFF.001-07.xlsx
+++ b/stories/arbres/ATOM-AUT.AFF.001-07.xlsx
@@ -841,7 +841,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Aniss veut l'oiseau du bois. Le chapeau tombe, le doudou est sur la chaise. Il range, marche, une plume lui chatouille le doigt.</t>
+          <t>Une ombre d'arbre entre dans la cuisine. Sur la vitre, un grain de pin colle. Aniss veut la plume grise sous l'arbre, maintenant, dans sa boîte. Il pousse tout dans le sac : le zip mord le chapeau. Il refuse de forcer, range une chose puis l'autre, glisse le grain. Sur le chemin, une branche barre le pas. Il refuse de foncer. Sous l'arbre, le grain de pin brille sur la plume.</t>
         </is>
       </c>
     </row>
@@ -1184,17 +1184,17 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Une branche frotte le chemin du bois. Les aiguilles de pin sentent le chaud. Une tartine croustille sur l'assiette. Ça sent le beurre. Un oiseau chante déjà dehors. Les crochets cliquettent un peu. Le tapis de l'entrée est un peu rêche. Une miette tombe près de la tasse. Papa verse un peu d'eau. L'eau fait un bruit clair. La tartine a un bord doré. Elle croustille, papa. Une dernière bouchée ? Oui. Aniss, tu entends l'oiseau ? Oui, je veux le voir dans le bois. On y va, avec le sac. En ce moment, Aniss s'accroupit. Le sac est posé contre la porte. Il est un peu froid. Le sac est bleu. Prends de l'eau, le chemin est long. Aniss prend la gourde. Elle est fraîche. Il la met dans le sac. Le chapeau aussi, les branches piquent. Aniss prend le chapeau. Le bord est un peu souple. Le chapeau glisse par terre. Il est tombé. Tu le ramasses, puis dans le sac. Aniss ramasse le chapeau. Il le met dans le sac. Et le doudou ? Le doudou n'est pas près des chaussures. Regarde la chaise de la cuisine.</t>
+          <t>Une ombre d'arbre entre dans la cuisine. Elle glisse sur la nappe, puis la tasse. Aniss lève les yeux vers la fenêtre. Les planches sentent la résine, tiède. Pourtant, un détail paraît nouveau. Une pomme de pin s'est ouverte sur le rebord. Un grain de pin colle à la vitre. Il est brun, collant, et il sent le bois. Il est tout petit, papa. C'est un grain tombé du pin. Le grain brille comme un bout d'étoile. Dehors, le grand arbre penche vers le chemin. Une plume grise tremble dans l'herbe, au loin. Je veux cette plume, maintenant ! Aniss, tu vois l'arbre ? Oui, papa. Elle m'attend. On y va, avec le sac. En ce moment, Aniss saisit le sac bleu. Le tissu gratte sous ses doigts. Prends de l'eau, pour le chemin. Aniss prend la gourde fraîche. Le bouchon est froid sous le doigt. Le chapeau aussi, les branches piquent. Aniss prend le chapeau souple. Le bord plie un peu, dans sa main. Et ma boîte à plumes ? La boîte de bois attend sur le banc. Je mets tout, d'un coup ! Il pousse gourde, chapeau et boîte. La boîte tape le fond, trop vite. Le zip mord le bord du chapeau. Ça reste coincé ! Le sourire d'Aniss disparaît. Dans sa poitrine, l'envie et l'inquiétude se bousculent. Tu regardes le zip ?</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Une branche frotte le chemin du bois. Les aiguilles de pin sentent le chaud. Une tartine croustille sur l'assiette. Ça sent le beurre. Un oiseau chante déjà dehors. Les crochets cliquettent un peu. Le tapis de l'entrée est un peu rêche. Une miette tombe près de la tasse. Papa verse un peu d'eau. L'eau fait un bruit clair. La tartine a un bord doré. Elle croustille, papa. Une dernière bouchée ? Oui. Aniss, tu entends l'oiseau ? Oui, je veux le voir dans le bois. On y va, avec le sac. En ce moment, Aniss s'accroupit. Le sac est posé contre la porte. Il est un peu froid. Le sac est bleu. Prends de l'eau, le chemin est long. Aniss prend la gourde. Elle est fraîche. Il la met dans le sac. Le chapeau aussi, les branches piquent. Aniss prend le chapeau. Le bord est un peu souple. Le chapeau glisse par terre. Il est tombé. Tu le ramasses, puis dans le sac. Aniss ramasse le chapeau. Il le met dans le sac. Et le doudou ? Le doudou n'est pas près des chaussures. Regarde la chaise de la cuisine.</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Une ombre d'arbre entre dans la cuisine. Elle glisse sur la nappe, puis la tasse. Aniss lève les yeux vers la fenêtre. Les planches sentent la résine, tiède. Pourtant, un détail paraît nouveau. Une pomme de pin s'est ouverte sur le rebord. Un &lt;emphasis level="moderate"&gt;grain de pin&lt;/emphasis&gt; colle à la vitre. Il est brun, collant, et il sent le bois. Il est tout petit, papa. C'est un grain tombé du pin. Le grain brille comme un bout d'étoile. Dehors, le grand arbre penche vers le chemin. Une plume grise tremble dans l'herbe, au loin. Je veux cette plume, maintenant ! Aniss, tu vois l'arbre ? Oui, papa. Elle m'attend. On y va, avec le sac. En ce moment, Aniss saisit le sac bleu. Le tissu gratte sous ses doigts. Prends de l'eau, pour le chemin. Aniss prend la gourde fraîche. Le bouchon est froid sous le doigt. Le chapeau aussi, les branches piquent. Aniss prend le chapeau souple. Le bord plie un peu, dans sa main. Et ma boîte à plumes ? La boîte de bois attend sur le banc. Je mets tout, d'un coup ! Il pousse gourde, chapeau et boîte. La boîte tape le fond, trop vite. Le zip mord le bord du chapeau. Ça reste coincé ! Le sourire d'Aniss disparaît. Dans sa poitrine, l'envie et l'inquiétude se bousculent. Tu regardes le zip ?&lt;/prosody&gt;&lt;break time="500ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Clara va au parc avec papa. Papa pose le &lt;emphasis&gt;sac&lt;/emphasis&gt; ouvert. Papa dit : on met la gourde. On met le chapeau. On met le doudou. C'est ce que l'adulte a dit. Clara prend la gourde. Elle la met dans le sac. Le sac est bleu. Clara prend le chapeau. Elle le met dans le sac. Elle prend le doudou. Elle le met dans le sac. Papa dit : tu as mis ce que l'adulte a dit. Clara ferme le sac. Elle le porte. À l'entrée, elle vérifie. Gourde, chapeau, doudou. Tout est dans le sac. Papa sourit. Clara a préparé son sac. [pause]</t>
+          <t>Une ombre d'arbre entre dans la cuisine. Elle glisse sur la nappe, puis la tasse. Aniss lève les yeux vers la fenêtre. Les planches sentent la résine, tiède. Pourtant, un détail paraît nouveau. Une pomme de pin s'est ouverte sur le rebord. Un &lt;emphasis&gt;grain de pin&lt;/emphasis&gt; colle à la vitre. Il est brun, collant, et il sent le bois. Il est tout petit, papa. C'est un grain tombé du pin. Le grain brille comme un bout d'étoile. Dehors, le grand arbre penche vers le chemin. Une plume grise tremble dans l'herbe, au loin. Je veux cette plume, maintenant ! Aniss, tu vois l'arbre ? Oui, papa. Elle m'attend. On y va, avec le sac. En ce moment, Aniss saisit le sac bleu. Le tissu gratte sous ses doigts. Prends de l'eau, pour le chemin. Aniss prend la gourde fraîche. Le bouchon est froid sous le doigt. Le chapeau aussi, les branches piquent. Aniss prend le chapeau souple. Le bord plie un peu, dans sa main. Et ma boîte à plumes ? La boîte de bois attend sur le banc. Je mets tout, d'un coup ! Il pousse gourde, chapeau et boîte. La boîte tape le fond, trop vite. Le zip mord le bord du chapeau. Ça reste coincé ! Le sourire d'Aniss disparaît. Dans sa poitrine, l'envie et l'inquiétude se bousculent. Tu regardes le zip ? [pause]</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr"/>
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="Y2" s="2" t="n">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
@@ -1249,10 +1249,10 @@
         </is>
       </c>
       <c r="AA2" s="2" t="n">
-        <v>0.92</v>
+        <v>0.98</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.22</v>
+        <v>1.12</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1275,30 +1275,30 @@
       </c>
       <c r="AH2" s="2" t="inlineStr">
         <is>
-          <t>sac</t>
+          <t>grain de pin</t>
         </is>
       </c>
       <c r="AI2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AJ2" s="2" t="n">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="AK2" s="2" t="n">
-        <v>280</v>
+        <v>260</v>
       </c>
       <c r="AL2" s="2" t="inlineStr">
         <is>
-          <t>calm</t>
+          <t>warm</t>
         </is>
       </c>
       <c r="AM2" s="2" t="inlineStr">
         <is>
-          <t>level</t>
+          <t>storytelling</t>
         </is>
       </c>
       <c r="AN2" s="2" t="n">
-        <v>0.333</v>
+        <v>0.36</v>
       </c>
       <c r="AO2" s="2" t="inlineStr"/>
       <c r="AP2" s="2" t="inlineStr">
@@ -1307,10 +1307,10 @@
         </is>
       </c>
       <c r="AQ2" s="2" t="n">
-        <v>0.92</v>
+        <v>0.98</v>
       </c>
       <c r="AR2" s="2" t="n">
-        <v>0.92</v>
+        <v>0.98</v>
       </c>
       <c r="AS2" s="2" t="n">
         <v>100</v>
@@ -1321,50 +1321,54 @@
       <c r="AU2" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AV2" s="2" t="inlineStr">
+        <is>
+          <t>arc=installation; intention=émerveiller puis tendre; emotion=impatience puis découragement; intensite=2; destinataire=enfant; sous_texte=il_veut_la_plume_maintenant; tempo=naturel puis resserré; sourire=léger puis aucun; respiration=ample puis retenue</t>
+        </is>
+      </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Une branche frotte le chemin du bois.
-narrateur|Les aiguilles de pin sentent le chaud.
-narrateur|Une tartine croustille sur l'assiette.
-narrateur|Ça sent le beurre.
-narrateur|Un oiseau chante déjà dehors.
-narrateur|Les crochets cliquettent un peu.
-narrateur|Le tapis de l'entrée est un peu rêche.
-narrateur|Une miette tombe près de la tasse.
-narrateur|Papa verse un peu d'eau.
-narrateur|L'eau fait un bruit clair.
-narrateur|La tartine a un bord doré.
-enfant-m|Elle croustille, papa.
-papa|Une dernière bouchée ?
-enfant-m|Oui.
-papa|Aniss, tu entends l'oiseau ?
-enfant-m|Oui, je veux le voir dans le bois.
+          <t>narrateur|Une ombre d'arbre entre dans la cuisine.
+narrateur|Elle glisse sur la nappe, puis la tasse.
+narrateur|Aniss lève les yeux vers la fenêtre.
+narrateur|Les planches sentent la résine, tiède.
+narrateur|Pourtant, un détail paraît nouveau.
+narrateur|Une pomme de pin s'est ouverte sur le rebord.
+narrateur|Un grain de pin colle à la vitre.
+narrateur|Il est brun, collant, et il sent le bois.
+enfant-m|Il est tout petit, papa.
+papa|C'est un grain tombé du pin.
+narrateur|Le grain brille comme un bout d'étoile.
+narrateur|Dehors, le grand arbre penche vers le chemin.
+narrateur|Une plume grise tremble dans l'herbe, au loin.
+enfant-m|Je veux cette plume, maintenant !
+papa|Aniss, tu vois l'arbre ?
+enfant-m|Oui, papa.
+enfant-m|Elle m'attend.
 papa|On y va, avec le sac.
-narrateur|En ce moment, Aniss s'accroupit.
-narrateur|Le sac est posé contre la porte.
-narrateur|Il est un peu froid.
-narrateur|Le sac est bleu.
-papa|Prends de l'eau, le chemin est long.
-narrateur|Aniss prend la gourde.
-narrateur|Elle est fraîche.
-narrateur|Il la met dans le sac.
+narrateur|En ce moment, Aniss saisit le sac bleu.
+narrateur|Le tissu gratte sous ses doigts.
+papa|Prends de l'eau, pour le chemin.
+narrateur|Aniss prend la gourde fraîche.
+narrateur|Le bouchon est froid sous le doigt.
 papa|Le chapeau aussi, les branches piquent.
-narrateur|Aniss prend le chapeau.
-narrateur|Le bord est un peu souple.
-narrateur|Le chapeau glisse par terre.
-enfant-m|Il est tombé.
-papa|Tu le ramasses, puis dans le sac.
-narrateur|Aniss ramasse le chapeau.
-narrateur|Il le met dans le sac.
-enfant-m|Et le doudou ?
-narrateur|Le doudou n'est pas près des chaussures.
-papa|Regarde la chaise de la cuisine.</t>
+narrateur|Aniss prend le chapeau souple.
+narrateur|Le bord plie un peu, dans sa main.
+enfant-m|Et ma boîte à plumes ?
+narrateur|La boîte de bois attend sur le banc.
+enfant-m|Je mets tout, d'un coup !
+narrateur|Il pousse gourde, chapeau et boîte.
+narrateur|La boîte tape le fond, trop vite.
+narrateur|Le zip mord le bord du chapeau.
+enfant-m|Ça reste coincé !
+narrateur|Le sourire d'Aniss disparaît.
+narrateur|Dans sa poitrine, l'envie et l'inquiétude se bousculent.
+papa|Tu regardes le zip ?</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>oiseau</t>
+          <t>pin,vitre,sac</t>
         </is>
       </c>
     </row>
@@ -1396,12 +1400,12 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Aniss prépare le sac. Où met-il les affaires ?</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Aniss prépare le &lt;emphasis level="moderate"&gt;sac&lt;/emphasis&gt;. Où met-il les affaires ?&lt;/prosody&gt;&lt;break time="700ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>&lt;slow&gt;Clara prépare le &lt;emphasis&gt;sac&lt;/emphasis&gt;. Que met-elle ?&lt;/slow&gt;</t>
+          <t>&lt;soft&gt;&lt;slow&gt;Aniss prépare le &lt;emphasis&gt;sac&lt;/emphasis&gt;. Où met-il les affaires ?&lt;/slow&gt;&lt;/soft&gt; [pause]</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -1464,7 +1468,7 @@
         </is>
       </c>
       <c r="Y3" s="2" t="n">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
@@ -1475,7 +1479,7 @@
         <v>0.86</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1490,11 +1494,11 @@
       <c r="AE3" s="2" t="inlineStr"/>
       <c r="AF3" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>soft</t>
         </is>
       </c>
       <c r="AG3" s="2" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AH3" s="2" t="inlineStr">
         <is>
@@ -1505,23 +1509,23 @@
         <v>200</v>
       </c>
       <c r="AJ3" s="2" t="n">
-        <v>250</v>
+        <v>700</v>
       </c>
       <c r="AK3" s="2" t="n">
-        <v>280</v>
+        <v>320</v>
       </c>
       <c r="AL3" s="2" t="inlineStr">
         <is>
-          <t>warm</t>
+          <t>focused</t>
         </is>
       </c>
       <c r="AM3" s="2" t="inlineStr">
         <is>
-          <t>rise</t>
+          <t>rising</t>
         </is>
       </c>
       <c r="AN3" s="2" t="n">
-        <v>0.333</v>
+        <v>0.32</v>
       </c>
       <c r="AO3" s="2" t="inlineStr"/>
       <c r="AP3" s="2" t="inlineStr">
@@ -1536,17 +1540,17 @@
         <v>0.86</v>
       </c>
       <c r="AS3" s="2" t="n">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="AT3" s="2" t="n">
         <v>50</v>
       </c>
       <c r="AU3" s="2" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AV3" s="2" t="inlineStr">
         <is>
-          <t>question d'écoute, ne change pas le cours</t>
+          <t>arc=indice; intention=faire_deviner; emotion=attention; intensite=1; destinataire=enfant; sous_texte=les_affaires_vont_dans_le_sac; tempo=suspendu; sourire=aucun; respiration=courte_avant_question</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
@@ -1579,17 +1583,17 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Le doudou est sur la chaise de la cuisine. Il sent le coton. Il est tout doux. Aniss le met dans le sac. Te voilà. Merci, Aniss. Aniss ferme le sac. Ça fait zzz. Il le porte. Le sac est prêt ? Oui, papa. La sangle n'est plus froide. Tu as fini ta tartine ? Oui, papa. Alors on va voir l'oiseau. Une miette reste près de la tasse. On la laisse pour plus tard.</t>
+          <t>Papa s'accroupit à la même hauteur. Aniss refuse de tirer plus fort. Je sors le chapeau. Il tire le tissu coincé, sans forcer. Le zip lâche, petit à petit. Il pose le chapeau à plat, sur la table. L'eau va au fond. Aniss range la gourde froide. La boîte de bois glisse à côté. Et mon doudou ? Le doudou n'est pas près des chaussures. Regarde le banc sous la fenêtre. Aniss cherche près du banc. Le doudou sent le coton, un peu chaud. Te voilà. Il le glisse dans le sac. Merci, Aniss. Le zip avance, sans mordre. Il part. Le sac est prêt ? Pas le grain. Tu prends aussi le grain de pin ? Oui, pour la plume. Aniss détache le grain de la vitre. Il le pose dans la boîte de bois. Aniss appuie sur la fermeture. Ça fait un petit zzz. Le sac bleu est fermé.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Le doudou est sur la chaise de la cuisine. Il sent le coton. Il est tout doux. Aniss le met dans le sac. Te voilà. Merci, Aniss. Aniss ferme le sac. Ça fait zzz. Il le porte. Le sac est prêt ? Oui, papa. La sangle n'est plus froide. Tu as fini ta tartine ? Oui, papa. Alors on va voir l'oiseau. Une miette reste près de la tasse. On la laisse pour plus tard.</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Papa s'accroupit à la même hauteur. Aniss refuse de tirer plus fort. Je sors le chapeau. Il tire le tissu coincé, sans forcer. Le zip lâche, petit à petit. Il pose le chapeau à plat, sur la table. L'eau va au fond. Aniss range la gourde froide. La boîte de bois glisse à côté. Et mon doudou ? Le doudou n'est pas près des chaussures. Regarde le banc sous la fenêtre. Aniss cherche près du banc. Le doudou sent le coton, un peu chaud. Te voilà. Il le glisse dans le &lt;emphasis level="moderate"&gt;sac&lt;/emphasis&gt;. Merci, Aniss. Le zip avance, sans mordre. Il part. Le sac est prêt ? Pas le grain. Tu prends aussi le grain de pin ? Oui, pour la plume. Aniss détache le grain de la vitre. Il le pose dans la boîte de bois. Aniss appuie sur la fermeture. Ça fait un petit zzz. Le sac bleu est fermé.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Clara a préparé son &lt;emphasis&gt;sac&lt;/emphasis&gt;. Elle a mis ce que l'adulte a dit. Papa était là. [pause]</t>
+          <t>Papa s'accroupit à la même hauteur. Aniss refuse de tirer plus fort. Je sors le chapeau. Il tire le tissu coincé, sans forcer. Le zip lâche, petit à petit. Il pose le chapeau à plat, sur la table. L'eau va au fond. Aniss range la gourde froide. La boîte de bois glisse à côté. Et mon doudou ? Le doudou n'est pas près des chaussures. Regarde le banc sous la fenêtre. Aniss cherche près du banc. Le doudou sent le coton, un peu chaud. Te voilà. Il le glisse dans le &lt;emphasis&gt;sac&lt;/emphasis&gt;. Merci, Aniss. Le zip avance, sans mordre. Il part. Le sac est prêt ? Pas le grain. Tu prends aussi le grain de pin ? Oui, pour la plume. Aniss détache le grain de la vitre. Il le pose dans la boîte de bois. Aniss appuie sur la fermeture. Ça fait un petit zzz. Le sac bleu est fermé. [pause]</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr"/>
@@ -1647,7 +1651,7 @@
         <v>0.92</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1684,16 +1688,16 @@
       </c>
       <c r="AL4" s="2" t="inlineStr">
         <is>
-          <t>calm</t>
+          <t>bright</t>
         </is>
       </c>
       <c r="AM4" s="2" t="inlineStr">
         <is>
-          <t>level</t>
+          <t>falling</t>
         </is>
       </c>
       <c r="AN4" s="2" t="n">
-        <v>0.333</v>
+        <v>0.34</v>
       </c>
       <c r="AO4" s="2" t="inlineStr"/>
       <c r="AP4" s="2" t="inlineStr">
@@ -1718,28 +1722,44 @@
       </c>
       <c r="AV4" s="2" t="inlineStr">
         <is>
-          <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
+          <t>arc=confirmation; intention=faire_vivre_le_geste; emotion=concentration puis fierté_calme; intensite=2; destinataire=enfant; sous_texte=une_chose_puis_la_suivante; tempo=naturel; sourire=léger; respiration=fluide</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Le doudou est sur la chaise de la cuisine.
-narrateur|Il sent le coton.
-narrateur|Il est tout doux.
-narrateur|Aniss le met dans le sac.
+          <t>narrateur|Papa s'accroupit à la même hauteur.
+narrateur|Aniss refuse de tirer plus fort.
+enfant-m|Je sors le chapeau.
+narrateur|Il tire le tissu coincé, sans forcer.
+narrateur|Le zip lâche, petit à petit.
+narrateur|Il pose le chapeau à plat, sur la table.
+papa|L'eau va au fond.
+narrateur|Aniss range la gourde froide.
+narrateur|La boîte de bois glisse à côté.
+enfant-m|Et mon doudou ?
+narrateur|Le doudou n'est pas près des chaussures.
+papa|Regarde le banc sous la fenêtre.
+narrateur|Aniss cherche près du banc.
+narrateur|Le doudou sent le coton, un peu chaud.
 enfant-m|Te voilà.
+narrateur|Il le glisse dans le sac.
 papa|Merci, Aniss.
-narrateur|Aniss ferme le sac.
-narrateur|Ça fait zzz.
-narrateur|Il le porte.
+narrateur|Le zip avance, sans mordre.
+enfant-m|Il part.
 papa|Le sac est prêt ?
-enfant-m|Oui, papa.
-narrateur|La sangle n'est plus froide.
-papa|Tu as fini ta tartine ?
-enfant-m|Oui, papa.
-papa|Alors on va voir l'oiseau.
-narrateur|Une miette reste près de la tasse.
-papa|On la laisse pour plus tard.</t>
+enfant-m|Pas le grain.
+papa|Tu prends aussi le grain de pin ?
+enfant-m|Oui, pour la plume.
+narrateur|Aniss détache le grain de la vitre.
+narrateur|Il le pose dans la boîte de bois.
+narrateur|Aniss appuie sur la fermeture.
+narrateur|Ça fait un petit zzz.
+narrateur|Le sac bleu est fermé.</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>zip,tissu</t>
         </is>
       </c>
     </row>
@@ -1766,17 +1786,17 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>On met tes chaussures. Aniss enfile ses chaussures. Tu as fini tes chaussures ? Oui, papa. On ouvre la porte. Papa ouvre la porte. L'air sent le pin et l'herbe sèche. L'oiseau chante encore. Je l'entends, papa. Oui, il est dans le grand arbre. Ils marchent sur le chemin du bois. Le sac tape doucement. La tartine n'est plus sur l'assiette. Ils s'arrêtent sous le grand arbre. Une feuille bouge. Il est là-haut. Oui, on écoute encore un peu. L'oiseau fait un petit cri. Aniss lève le menton. Une plume grise est dans l'herbe. Pour moi ? Tu la prends tout doux ? Aniss ramasse la plume. Elle est légère, presque rien.</t>
+          <t>On met tes chaussures ? Aniss enfile ses chaussures. Une semelle est froide, contre le sol. Tu as fini tes chaussures ? Oui, papa. On ouvre la porte. Papa ouvre la porte. L'air sent la résine et l'herbe sèche. Le sac bleu tape contre sa hanche. On va voir la plume ? Oui, sous le grand arbre. Ils marchent sur le chemin du bois. Les aiguilles de pin craquent sous les pas. Je la vois, papa ! Une plume grise brille, plus loin. Je cours la prendre ! Aniss veut partir sans le sac. Une branche basse barre le pas. Le sourire d'Aniss se serre. Ça serre, dans son ventre. Je n'aime pas ça. Aniss refuse de foncer. Attends, je regarde. Personne ne donne la réponse. Aniss observe le sac, écoute le bois. Dans la boîte, le grain de pin a bougé. Il penche vers la branche basse. C'est par là. Tu contournes, ou tu pousses ? Je contourne. Il recule d'un pas. Il passe sous la branche, lentement. Le sac reste bien fermé. Elle est là. Oui, dans l'herbe.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>On met tes chaussures. Aniss enfile ses chaussures. Tu as fini tes chaussures ? Oui, papa. On ouvre la porte. Papa ouvre la porte. L'air sent le pin et l'herbe sèche. L'oiseau chante encore. Je l'entends, papa. Oui, il est dans le grand arbre. Ils marchent sur le chemin du bois. Le sac tape doucement. La tartine n'est plus sur l'assiette. Ils s'arrêtent sous le grand arbre. Une feuille bouge. Il est là-haut. Oui, on écoute encore un peu. L'oiseau fait un petit cri. Aniss lève le menton. Une plume grise est dans l'herbe. Pour moi ? Tu la prends tout doux ? Aniss ramasse la plume. Elle est légère, presque rien.</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;On met tes chaussures ? Aniss enfile ses chaussures. Une semelle est froide, contre le sol. Tu as fini tes chaussures ? Oui, papa. On ouvre la porte. Papa ouvre la porte. L'air sent la résine et l'herbe sèche. Le sac bleu tape contre sa hanche. On va voir la plume ? Oui, sous le grand arbre. Ils marchent sur le chemin du bois. Les aiguilles de pin craquent sous les pas. Je la vois, papa ! Une plume grise brille, plus loin. Je cours la prendre ! Aniss veut partir sans le sac. Une branche basse barre le pas. Le sourire d'Aniss se serre. Ça serre, dans son ventre. Je n'aime pas ça. Aniss refuse de foncer. Attends, je regarde. Personne ne donne la réponse. Aniss observe le sac, écoute le bois. Dans la boîte, le &lt;emphasis level="moderate"&gt;grain de pin&lt;/emphasis&gt; a bougé. Il penche vers la branche basse. C'est par là. Tu contournes, ou tu pousses ? Je contourne. Il recule d'un pas. Il passe sous la branche, lentement. Le sac reste bien fermé. Elle est là. Oui, dans l'herbe.&lt;/prosody&gt;&lt;break time="420ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Clara porte le &lt;emphasis&gt;sac&lt;/emphasis&gt;. Papa ouvre la porte. [pause]</t>
+          <t>On met tes chaussures ? Aniss enfile ses chaussures. Une semelle est froide, contre le sol. Tu as fini tes chaussures ? Oui, papa. On ouvre la porte. Papa ouvre la porte. L'air sent la résine et l'herbe sèche. Le sac bleu tape contre sa hanche. On va voir la plume ? Oui, sous le grand arbre. Ils marchent sur le chemin du bois. Les aiguilles de pin craquent sous les pas. Je la vois, papa ! Une plume grise brille, plus loin. Je cours la prendre ! Aniss veut partir sans le sac. Une branche basse barre le pas. Le sourire d'Aniss se serre. Ça serre, dans son ventre. Je n'aime pas ça. Aniss refuse de foncer. Attends, je regarde. Personne ne donne la réponse. Aniss observe le sac, écoute le bois. Dans la boîte, le &lt;emphasis&gt;grain de pin&lt;/emphasis&gt; a bougé. Il penche vers la branche basse. C'est par là. Tu contournes, ou tu pousses ? Je contourne. Il recule d'un pas. Il passe sous la branche, lentement. Le sac reste bien fermé. Elle est là. Oui, dans l'herbe. [pause]</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr"/>
@@ -1823,7 +1843,7 @@
         </is>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>132</v>
+        <v>146</v>
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
@@ -1831,10 +1851,10 @@
         </is>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1857,30 +1877,30 @@
       </c>
       <c r="AH5" s="2" t="inlineStr">
         <is>
-          <t>sac</t>
+          <t>grain de pin</t>
         </is>
       </c>
       <c r="AI5" s="2" t="n">
         <v>200</v>
       </c>
       <c r="AJ5" s="2" t="n">
-        <v>450</v>
+        <v>420</v>
       </c>
       <c r="AK5" s="2" t="n">
-        <v>280</v>
+        <v>250</v>
       </c>
       <c r="AL5" s="2" t="inlineStr">
         <is>
-          <t>calm</t>
+          <t>lively</t>
         </is>
       </c>
       <c r="AM5" s="2" t="inlineStr">
         <is>
-          <t>level</t>
+          <t>dynamic</t>
         </is>
       </c>
       <c r="AN5" s="2" t="n">
-        <v>0.333</v>
+        <v>0.37</v>
       </c>
       <c r="AO5" s="2" t="inlineStr"/>
       <c r="AP5" s="2" t="inlineStr">
@@ -1889,10 +1909,10 @@
         </is>
       </c>
       <c r="AQ5" s="2" t="n">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="AR5" s="2" t="n">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="AS5" s="2" t="n">
         <v>100</v>
@@ -1903,33 +1923,53 @@
       <c r="AU5" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AV5" s="2" t="inlineStr">
+        <is>
+          <t>arc=action; intention=entraîner; emotion=élan puis prudence; intensite=2; destinataire=enfant; sous_texte=il_refuse_de_foncer_sous_la_branche; tempo=vif puis posé; sourire=léger; respiration=courte</t>
+        </is>
+      </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>papa|On met tes chaussures.
+          <t>papa|On met tes chaussures ?
 narrateur|Aniss enfile ses chaussures.
+narrateur|Une semelle est froide, contre le sol.
 papa|Tu as fini tes chaussures ?
 enfant-m|Oui, papa.
 papa|On ouvre la porte.
 narrateur|Papa ouvre la porte.
-narrateur|L'air sent le pin et l'herbe sèche.
-narrateur|L'oiseau chante encore.
-enfant-m|Je l'entends, papa.
-papa|Oui, il est dans le grand arbre.
+narrateur|L'air sent la résine et l'herbe sèche.
+narrateur|Le sac bleu tape contre sa hanche.
+enfant-m|On va voir la plume ?
+papa|Oui, sous le grand arbre.
 narrateur|Ils marchent sur le chemin du bois.
-narrateur|Le sac tape doucement.
-narrateur|La tartine n'est plus sur l'assiette.
-narrateur|Ils s'arrêtent sous le grand arbre.
-narrateur|Une feuille bouge.
-enfant-m|Il est là-haut.
-papa|Oui, on écoute encore un peu.
-narrateur|L'oiseau fait un petit cri.
-narrateur|Aniss lève le menton.
-narrateur|Une plume grise est dans l'herbe.
-enfant-m|Pour moi ?
-papa|Tu la prends tout doux ?
-narrateur|Aniss ramasse la plume.
-narrateur|Elle est légère, presque rien.</t>
+narrateur|Les aiguilles de pin craquent sous les pas.
+enfant-m|Je la vois, papa !
+narrateur|Une plume grise brille, plus loin.
+enfant-m|Je cours la prendre !
+narrateur|Aniss veut partir sans le sac.
+narrateur|Une branche basse barre le pas.
+narrateur|Le sourire d'Aniss se serre.
+narrateur|Ça serre, dans son ventre.
+enfant-m|Je n'aime pas ça.
+narrateur|Aniss refuse de foncer.
+enfant-m|Attends, je regarde.
+narrateur|Personne ne donne la réponse.
+narrateur|Aniss observe le sac, écoute le bois.
+narrateur|Dans la boîte, le grain de pin a bougé.
+narrateur|Il penche vers la branche basse.
+enfant-m|C'est par là.
+papa|Tu contournes, ou tu pousses ?
+enfant-m|Je contourne.
+narrateur|Il recule d'un pas.
+narrateur|Il passe sous la branche, lentement.
+narrateur|Le sac reste bien fermé.
+enfant-m|Elle est là.
+papa|Oui, dans l'herbe.</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>chemin,branches</t>
         </is>
       </c>
     </row>
@@ -1956,17 +1996,17 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>La plume chatouille le doigt d'Aniss. L'oiseau chante plus fort. On l'a vu. On l'a entendu. Le sac voyage sur le dos d'Aniss. Les aiguilles de pin sentent encore le chaud. Le doudou est chaud, contre toi. Aniss reste un moment, tout calme, sous l'arbre.</t>
+          <t>Ils s'arrêtent sous le grand arbre. L'ombre de l'arbre touche les joues d'Aniss. La plume est là. Oui, elle t'attendait. Une plume grise repose dans l'herbe sèche. Sur la plume, un grain de pin brille. Comme sur la vitre, papa ! Tu la prends, toi ? Oui, dans ma boîte. Aniss ouvre le sac, sans se presser. Il glisse la plume contre le grain de pin. Le grain colle un peu à la plume. Ils voyagent ensemble. Tu les sens, sur tes doigts ? Oui, ça sent le bois. Le sac repose contre sa hanche. Le grain de pin brille sur la plume.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>La plume chatouille le doigt d'Aniss. L'oiseau chante plus fort. On l'a vu. On l'a entendu. Le sac voyage sur le dos d'Aniss. Les aiguilles de pin sentent encore le chaud. Le doudou est chaud, contre toi. Aniss reste un moment, tout calme, sous l'arbre.</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Ils s'arrêtent sous le grand arbre. L'ombre de l'arbre touche les joues d'Aniss. La plume est là. Oui, elle t'attendait. Une plume grise repose dans l'herbe sèche. Sur la plume, un &lt;emphasis level="moderate"&gt;grain de pin&lt;/emphasis&gt; brille. Comme sur la vitre, papa ! Tu la prends, toi ? Oui, dans ma boîte. Aniss ouvre le sac, sans se presser. Il glisse la plume contre le grain de pin. Le grain colle un peu à la plume. Ils voyagent ensemble. Tu les sens, sur tes doigts ? Oui, ça sent le bois. Le sac repose contre sa hanche. Le grain de pin brille sur la plume.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>&lt;lower-pitch&gt;&lt;soft&gt;&lt;slow&gt;L'histoire est finie.&lt;/slow&gt;&lt;/soft&gt;&lt;/lower-pitch&gt; [pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Ils s'arrêtent sous le grand arbre. L'ombre de l'arbre touche les joues d'Aniss. La plume est là. Oui, elle t'attendait. Une plume grise repose dans l'herbe sèche. Sur la plume, un &lt;emphasis&gt;grain de pin&lt;/emphasis&gt; brille. Comme sur la vitre, papa ! Tu la prends, toi ? Oui, dans ma boîte. Aniss ouvre le sac, sans se presser. Il glisse la plume contre le grain de pin. Le grain colle un peu à la plume. Ils voyagent ensemble. Tu les sens, sur tes doigts ? Oui, ça sent le bois. Le sac repose contre sa hanche. Le grain de pin brille sur la plume.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr"/>
@@ -2013,18 +2053,18 @@
         </is>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>slow</t>
         </is>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>0.88</v>
+        <v>0.85</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2033,12 +2073,12 @@
       </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>-2st</t>
         </is>
       </c>
       <c r="AE6" s="2" t="inlineStr">
         <is>
-          <t>lower-pitch</t>
+          <t>low-pitch</t>
         </is>
       </c>
       <c r="AF6" s="2" t="inlineStr">
@@ -2047,17 +2087,21 @@
         </is>
       </c>
       <c r="AG6" s="2" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AH6" s="2" t="inlineStr"/>
+        <v>-3</v>
+      </c>
+      <c r="AH6" s="2" t="inlineStr">
+        <is>
+          <t>grain de pin</t>
+        </is>
+      </c>
       <c r="AI6" s="2" t="n">
         <v>200</v>
       </c>
       <c r="AJ6" s="2" t="n">
-        <v>600</v>
+        <v>900</v>
       </c>
       <c r="AK6" s="2" t="n">
-        <v>280</v>
+        <v>340</v>
       </c>
       <c r="AL6" s="2" t="inlineStr">
         <is>
@@ -2066,11 +2110,11 @@
       </c>
       <c r="AM6" s="2" t="inlineStr">
         <is>
-          <t>fall</t>
+          <t>falling</t>
         </is>
       </c>
       <c r="AN6" s="2" t="n">
-        <v>0.333</v>
+        <v>0.31</v>
       </c>
       <c r="AO6" s="2" t="inlineStr"/>
       <c r="AP6" s="2" t="inlineStr">
@@ -2079,31 +2123,49 @@
         </is>
       </c>
       <c r="AQ6" s="2" t="n">
-        <v>0.88</v>
+        <v>0.85</v>
       </c>
       <c r="AR6" s="2" t="n">
-        <v>0.88</v>
+        <v>0.85</v>
       </c>
       <c r="AS6" s="2" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AT6" s="2" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="AU6" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV6" s="2" t="inlineStr"/>
+        <v>12</v>
+      </c>
+      <c r="AV6" s="2" t="inlineStr">
+        <is>
+          <t>arc=retour; intention=refermer; emotion=tendresse et fierté_calme; intensite=1; destinataire=enfant; sous_texte=le_grain_de_la_vitre_est_sur_la_plume; tempo=posé; sourire=léger; respiration=ample</t>
+        </is>
+      </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|La plume chatouille le doigt d'Aniss.
-narrateur|L'oiseau chante plus fort.
-enfant-m|On l'a vu.
-papa|On l'a entendu.
-narrateur|Le sac voyage sur le dos d'Aniss.
-narrateur|Les aiguilles de pin sentent encore le chaud.
-papa|Le doudou est chaud, contre toi.
-narrateur|Aniss reste un moment, tout calme, sous l'arbre.</t>
+          <t>narrateur|Ils s'arrêtent sous le grand arbre.
+narrateur|L'ombre de l'arbre touche les joues d'Aniss.
+enfant-m|La plume est là.
+papa|Oui, elle t'attendait.
+narrateur|Une plume grise repose dans l'herbe sèche.
+narrateur|Sur la plume, un grain de pin brille.
+enfant-m|Comme sur la vitre, papa !
+papa|Tu la prends, toi ?
+enfant-m|Oui, dans ma boîte.
+narrateur|Aniss ouvre le sac, sans se presser.
+narrateur|Il glisse la plume contre le grain de pin.
+narrateur|Le grain colle un peu à la plume.
+enfant-m|Ils voyagent ensemble.
+papa|Tu les sens, sur tes doigts ?
+enfant-m|Oui, ça sent le bois.
+narrateur|Le sac repose contre sa hanche.
+narrateur|Le grain de pin brille sur la plume.</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>arbre,plume</t>
         </is>
       </c>
     </row>
@@ -2124,7 +2186,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A13"/>
+  <dimension ref="A1:A14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2216,6 +2278,13 @@
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
